--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_325_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_325_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M2" t="n">
         <v>15</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.29</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M3" t="n">
         <v>14</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1335,7 +1335,7 @@
         <v>21</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1733,10 +1733,10 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X19" t="n">
         <v>3</v>
@@ -2119,7 +2119,7 @@
         <v>4</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>5</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2707,16 +2707,16 @@
         <v>18</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X24" t="n">
         <v>6</v>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -3298,13 +3298,13 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X27" t="n">
         <v>5</v>
@@ -3827,16 +3827,16 @@
         <v>104</v>
       </c>
       <c r="T30" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X30" t="n">
         <v>25</v>
@@ -4295,7 +4295,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -4684,7 +4684,7 @@
         <v>16</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -4880,16 +4880,16 @@
         <v>10</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X38" t="n">
         <v>5</v>
@@ -5079,7 +5079,7 @@
         <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -5468,16 +5468,16 @@
         <v>6</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X41" t="n">
         <v>2</v>
@@ -5860,10 +5860,10 @@
         <v>1</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6056,16 +6056,16 @@
         <v>12</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X44" t="n">
         <v>5</v>
@@ -6255,7 +6255,7 @@
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>
@@ -6784,16 +6784,16 @@
         <v>93</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X48" t="n">
         <v>27</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_325_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_325_EL.xlsx
@@ -674,10 +674,10 @@
         <v>15</v>
       </c>
       <c r="N2" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="P2" t="n">
         <v>7</v>
@@ -695,17 +695,17 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V2" t="n">
         <v>9</v>
       </c>
       <c r="W2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>33.33</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>40.91</t>
+          <t>42.86</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.09</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>14</v>
       </c>
       <c r="N3" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="O3" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="P3" t="n">
         <v>5</v>
@@ -851,20 +851,20 @@
         <v>5</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="V3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W3" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>93.10</t>
+          <t>89.47</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -884,12 +884,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>30.43</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,14 +1347,14 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="Y17" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -1579,7 +1579,7 @@
         <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
@@ -1739,10 +1739,10 @@
         <v>3</v>
       </c>
       <c r="X19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
@@ -2719,10 +2719,10 @@
         <v>4</v>
       </c>
       <c r="X24" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -2915,14 +2915,14 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA25" t="n">
@@ -3111,14 +3111,14 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA26" t="n">
@@ -3307,14 +3307,14 @@
         <v>1</v>
       </c>
       <c r="X27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA27" t="n">
@@ -3839,14 +3839,14 @@
         <v>8</v>
       </c>
       <c r="X30" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="Y30" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3875,22 +3875,22 @@
         <v>1</v>
       </c>
       <c r="AH30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AJ30" t="n">
         <v>9</v>
       </c>
       <c r="AK30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4304,14 +4304,14 @@
         <v>0</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA35" t="n">
@@ -4696,14 +4696,14 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y37" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -4892,14 +4892,14 @@
         <v>2</v>
       </c>
       <c r="X38" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y38" t="n">
         <v>5</v>
       </c>
-      <c r="Y38" t="n">
-        <v>6</v>
-      </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -5121,25 +5121,25 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="AJ39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AK39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL39" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="AM39" t="inlineStr">
@@ -5480,10 +5480,10 @@
         <v>1</v>
       </c>
       <c r="X41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
@@ -6068,10 +6068,10 @@
         <v>1</v>
       </c>
       <c r="X44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Y44" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI44" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>0</v>
       </c>
       <c r="AK44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL44" t="inlineStr">
         <is>
@@ -6264,10 +6264,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
@@ -6796,14 +6796,14 @@
         <v>4</v>
       </c>
       <c r="X48" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="Y48" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>93.1%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="AA48" t="n">
@@ -6829,10 +6829,10 @@
         </is>
       </c>
       <c r="AG48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
@@ -6840,14 +6840,14 @@
         </is>
       </c>
       <c r="AJ48" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK48" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
